--- a/Tx_to_Rx_Cluster_Testcase.xlsx
+++ b/Tx_to_Rx_Cluster_Testcase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adity\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C80FD7A-ED1C-4BD1-8996-E94B0B885434}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F2AE6C7-C94A-4B87-B1CB-36D94E666280}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{7F5F1F97-6830-442D-B1A8-50EC1DB16EA5}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="50">
   <si>
     <t>DESCRIPTION</t>
   </si>
@@ -129,6 +129,96 @@
   <si>
     <t>1) Help of this test I want to verify payload
      range first</t>
+  </si>
+  <si>
+    <t>Tx_to_Rx_Cluster_Test_05</t>
+  </si>
+  <si>
+    <t>VALID_ADDRESS_SCENARIO</t>
+  </si>
+  <si>
+    <t>1) Verify normal frame with valid source and 
+     destination address</t>
+  </si>
+  <si>
+    <t>1) Apply source and destination address in range between
+     6 byte(48 bits)</t>
+  </si>
+  <si>
+    <t>Tx_to_Rx_Cluster_Test_06</t>
+  </si>
+  <si>
+    <t>VALID_SOURCE_ADDRESS_INVALID_DESTINATION
+_ADDRESS_SCENARIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Apply valid source address and invalid 
+    destination address check design responce                                               </t>
+  </si>
+  <si>
+    <t>1) Apply source address in range and destination address
+    out of range</t>
+  </si>
+  <si>
+    <t>Tx_to_Rx_Cluster_Test_07</t>
+  </si>
+  <si>
+    <t>INVALID_SOURCE_ADDRESS_VALID_DESTINATION
+_ADDRESS_SCENARIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Apply invalid source address and valid 
+    destination address check design responce </t>
+  </si>
+  <si>
+    <t>1) Apply source address in out of range and destination address
+    in range</t>
+  </si>
+  <si>
+    <t>Tx_to_Rx_Cluster_Test_08</t>
+  </si>
+  <si>
+    <t>INVALID_SOURCE_ADDRESS_INVALID_DESTINATION
+_ADDRESS_SCENARIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Apply invalid source address and invalid 
+    destination address check design responce </t>
+  </si>
+  <si>
+    <t>1) Apply both source address and destination address
+    out of range</t>
+  </si>
+  <si>
+    <t>Tx_to_Rx_Cluster_Test_09</t>
+  </si>
+  <si>
+    <t>VALID_ADDRESS_AND_INVALID_ETYPE_SCENARIO</t>
+  </si>
+  <si>
+    <t>1) Verify normal frame with valid source, 
+     destination address and invlid etype</t>
+  </si>
+  <si>
+    <t>1) Apply first sorce and destination address in valid range
+2) with apply invalid/corrupt etype</t>
+  </si>
+  <si>
+    <t>Tx_to_Rx_Cluster_Test_10</t>
+  </si>
+  <si>
+    <t>ADDRESS_BOUNDARY_SCENARIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Help of this test I want to verify address
+     range </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Apply MIN_RANGE_OF_SOURCE_ADDRESS
+2) Apply MAX_RANGE_OF_SOURCE_ADDRESS
+3) Apply MIN_RANGE_OF_DESTINATION_ADDRESS
+4) Apply MAX_RANGE_OF_DESTINATION_ADDRESS
+</t>
   </si>
 </sst>
 </file>
@@ -207,7 +297,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -235,6 +325,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -550,13 +643,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{095FC77F-B014-42C2-A56A-E9ABFE57B373}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.21875" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
+    <col min="2" max="2" width="52.6640625" customWidth="1"/>
     <col min="3" max="3" width="39.33203125" customWidth="1"/>
-    <col min="4" max="4" width="49" customWidth="1"/>
+    <col min="4" max="4" width="52.6640625" customWidth="1"/>
     <col min="5" max="5" width="15.77734375" customWidth="1"/>
     <col min="6" max="6" width="12.88671875" customWidth="1"/>
     <col min="7" max="7" width="23.44140625" customWidth="1"/>
@@ -655,6 +748,90 @@
       </c>
       <c r="D6" s="9" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
